--- a/test_data/servicenow_test.xlsx
+++ b/test_data/servicenow_test.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Configuration Item</t>
+          <t>Configuration item</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -452,7 +452,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Proposed By</t>
+          <t>Proposed by</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -472,12 +472,12 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>Actual Incident Resolve</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Actual Incident Start</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Actual Incident Resolve</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">

--- a/test_data/servicenow_test.xlsx
+++ b/test_data/servicenow_test.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
